--- a/public/exports-with-coowners/29189773.xlsx
+++ b/public/exports-with-coowners/29189773.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjtertoft 7</t>
+          <t xml:space="preserve">Flintholmvej 4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787622</t>
+          <t xml:space="preserve">5787788</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="J48">
-        <v>1001</v>
+        <v>1857</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009991</t>
+          <t xml:space="preserve">200010534</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">botjek Haderslev</t>
+          <t xml:space="preserve">Botjek Haderslev</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-01-15</t>
+          <t xml:space="preserve">2019-02-09</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholmvej 4</t>
+          <t xml:space="preserve">Storegade 14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787788</t>
+          <t xml:space="preserve">5785700</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>1857</v>
+        <v>336</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010534</t>
+          <t xml:space="preserve">200010697</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-09</t>
+          <t xml:space="preserve">2019-02-17</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 14</t>
+          <t xml:space="preserve">Tangsmose 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785700</t>
+          <t xml:space="preserve">5285761</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010697</t>
+          <t xml:space="preserve">200011492</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-17</t>
+          <t xml:space="preserve">2019-03-16</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangsmose 2</t>
+          <t xml:space="preserve">Bonderosevej 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285761</t>
+          <t xml:space="preserve">5285444</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="J51">
-        <v>364</v>
+        <v>1217</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011492</t>
+          <t xml:space="preserve">200011536</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Haderslev</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-16</t>
+          <t xml:space="preserve">2019-03-17</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bonderosevej 1</t>
+          <t xml:space="preserve">Kærvej 17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285444</t>
+          <t xml:space="preserve">5783138</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,21 +3885,21 @@
         </is>
       </c>
       <c r="J52">
-        <v>1217</v>
+        <v>1072</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011536</t>
+          <t xml:space="preserve">200011633</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek Haderslev</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-17</t>
+          <t xml:space="preserve">2019-03-18</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 17</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783138</t>
+          <t xml:space="preserve">5295266</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="J53">
-        <v>1072</v>
+        <v>9679</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011633</t>
+          <t xml:space="preserve">200012359</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-18</t>
+          <t xml:space="preserve">2019-04-07</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">B.S.Ingemanns Vej 3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295266</t>
+          <t xml:space="preserve">7967180</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="J54">
-        <v>9679</v>
+        <v>1682</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012359</t>
+          <t xml:space="preserve">200012502</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-07</t>
+          <t xml:space="preserve">2019-04-15</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S.Ingemanns Vej 3</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 100A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967180</t>
+          <t xml:space="preserve">5292892</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>1682</v>
+        <v>905</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012502</t>
+          <t xml:space="preserve">200012601</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-15</t>
+          <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 100A</t>
+          <t xml:space="preserve">Kongevej 35</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292892</t>
+          <t xml:space="preserve">1512218</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>905</v>
+        <v>6492</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012601</t>
+          <t xml:space="preserve">200014764</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-17</t>
+          <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 35</t>
+          <t xml:space="preserve">Stjernevej 63</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512218</t>
+          <t xml:space="preserve">5259087</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>6492</v>
+        <v>735</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014764</t>
+          <t xml:space="preserve">200016722</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-10</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stjernevej 63</t>
+          <t xml:space="preserve">Buskmosevej 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259087</t>
+          <t xml:space="preserve">5272978</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>735</v>
+        <v>499</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016722</t>
+          <t xml:space="preserve">200017325</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-09</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,40 +4391,40 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buskmosevej 2</t>
+          <t xml:space="preserve">Skydebanevej 4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272978</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J59">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017325</t>
+          <t xml:space="preserve">200018102</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Haderslev</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-09</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 10</t>
+          <t xml:space="preserve">Færgevej 68</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151738</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">100127221</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,40 +4541,40 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 4</t>
+          <t xml:space="preserve">Færgevej 70</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>529</v>
+        <v>274</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018102</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek Haderslev</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,30 +4616,30 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 68</t>
+          <t xml:space="preserve">Mågevænget 10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">5292814</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>573</v>
+        <v>4679</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200023568</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-11-08</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 70</t>
+          <t xml:space="preserve">Søvænget 7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">5787053</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>274</v>
+        <v>361</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200023607</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mågevænget 10</t>
+          <t xml:space="preserve">Lille Rådhusgade 10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,30 +4776,30 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292814</t>
+          <t xml:space="preserve">8111599</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>4679</v>
+        <v>329</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023568</t>
+          <t xml:space="preserve">200023651</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Haderslev</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-08</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvænget 7</t>
+          <t xml:space="preserve">Kær Bygade 19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787053</t>
+          <t xml:space="preserve">8917210</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>361</v>
+        <v>1325</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023607</t>
+          <t xml:space="preserve">200023827</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-09</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,30 +4916,30 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Rådhusgade 10</t>
+          <t xml:space="preserve">Avntoftvej 8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8111599</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J66">
-        <v>329</v>
+        <v>1717</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023651</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kær Bygade 19</t>
+          <t xml:space="preserve">Avntoftvej 8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917210</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J67">
-        <v>1325</v>
+        <v>624</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023827</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Haderslev</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,40 +5066,40 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avntoftvej 8</t>
+          <t xml:space="preserve">Ulbjerggade 29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">5787473</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>1717</v>
+        <v>296</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025499</t>
+          <t xml:space="preserve">200029940</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek Haderslev</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,30 +5141,30 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avntoftvej 8</t>
+          <t xml:space="preserve">Mejerivej 13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">7870345</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J69">
-        <v>624</v>
+        <v>579</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025499</t>
+          <t xml:space="preserve">200030269</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-04-13</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulbjerggade 29</t>
+          <t xml:space="preserve">A D Jørgensensgade 12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787473</t>
+          <t xml:space="preserve">5258778</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>296</v>
+        <v>525</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029940</t>
+          <t xml:space="preserve">200031045</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-31</t>
+          <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,40 +5291,40 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 13</t>
+          <t xml:space="preserve">Aabenraavej 25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870345</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J71">
-        <v>579</v>
+        <v>4816</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030269</t>
+          <t xml:space="preserve">310000776</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-13</t>
+          <t xml:space="preserve">2022-06-27</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A D Jørgensensgade 12</t>
+          <t xml:space="preserve">Svanehaven 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5258778</t>
+          <t xml:space="preserve">100019921</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,21 +5385,21 @@
         </is>
       </c>
       <c r="J72">
-        <v>525</v>
+        <v>7293</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031045</t>
+          <t xml:space="preserve">311005752</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Haderslev</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-04</t>
+          <t xml:space="preserve">2023-06-26</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraavej 25</t>
+          <t xml:space="preserve">Møllegade 54</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">8166350</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J73">
-        <v>4816</v>
+        <v>1494</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000776</t>
+          <t xml:space="preserve">311041979</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-27</t>
+          <t xml:space="preserve">2024-03-10</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanehaven 2</t>
+          <t xml:space="preserve">Nørre Havnegade 15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019921</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,31 +5535,31 @@
         </is>
       </c>
       <c r="J74">
-        <v>7293</v>
+        <v>1276</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311005752</t>
+          <t xml:space="preserve">311301220</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-26</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 54</t>
+          <t xml:space="preserve">Nørre Havnegade 15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,40 +5601,40 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8166350</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>1494</v>
+        <v>4367</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041979</t>
+          <t xml:space="preserve">311301223</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-10</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Havnegade 15</t>
+          <t xml:space="preserve">B.S.Ingemanns Vej 1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,30 +5676,30 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J76">
-        <v>1276</v>
+        <v>1740</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301220</t>
+          <t xml:space="preserve">311332174</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2028-08-23</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborg Kommune</t>
+          <t xml:space="preserve">Sundhedshus Gråsten ApS</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Havnegade 15</t>
+          <t xml:space="preserve">Ulsnæs 6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">313268, 313269, 313271, 313272, 313270</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="J77">
-        <v>4367</v>
+        <v>2352</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301223</t>
+          <t xml:space="preserve">311369806</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2029-04-08</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S.Ingemanns Vej 1</t>
+          <t xml:space="preserve">Præstegårdsvej 8A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,30 +5826,30 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">10185368</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>1740</v>
+        <v>984</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332174</t>
+          <t xml:space="preserve">311370738</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-23</t>
+          <t xml:space="preserve">2029-04-11</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundhedshus Gråsten ApS</t>
+          <t xml:space="preserve">Sønderborg Kommune</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5891,30 +5891,30 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulsnæs 6</t>
+          <t xml:space="preserve">Avnbølvej 12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">313268, 313269, 313271, 313272, 313270</t>
+          <t xml:space="preserve">9072481</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>2352</v>
+        <v>290</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369806</t>
+          <t xml:space="preserve">311373248</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-08</t>
+          <t xml:space="preserve">2029-04-26</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 8A</t>
+          <t xml:space="preserve">Kærvej 70</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">10185368</t>
+          <t xml:space="preserve">5783317</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,21 +5985,21 @@
         </is>
       </c>
       <c r="J80">
-        <v>984</v>
+        <v>1702</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311370738</t>
+          <t xml:space="preserve">311436294</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-11</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,40 +6041,40 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avnbølvej 12</t>
+          <t xml:space="preserve">Nørregade 11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072481</t>
+          <t xml:space="preserve">8583585</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J81">
-        <v>290</v>
+        <v>522</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373248</t>
+          <t xml:space="preserve">311498594</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-26</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 70</t>
+          <t xml:space="preserve">Stråbjergvej 1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783317</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>1702</v>
+        <v>6889</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436294</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-06</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,40 +6191,40 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11</t>
+          <t xml:space="preserve">Stråbjergvej 1A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8583585</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J83">
-        <v>522</v>
+        <v>1468</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498594</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 1</t>
+          <t xml:space="preserve">Stråbjergvej 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,15 +6281,15 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>6889</v>
+        <v>10229</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311521350</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 1A</t>
+          <t xml:space="preserve">Stråbjergvej 7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6356,15 +6356,15 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J85">
-        <v>1468</v>
+        <v>1157</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311521353</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 3</t>
+          <t xml:space="preserve">Skolevej 19A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>10229</v>
+        <v>261</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521350</t>
+          <t xml:space="preserve">311560181</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 7</t>
+          <t xml:space="preserve">Skolevej 19B</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J87">
-        <v>1157</v>
+        <v>689</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521353</t>
+          <t xml:space="preserve">311560185</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19A</t>
+          <t xml:space="preserve">Skolevej 21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6581,15 +6581,15 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
-        <v>261</v>
+        <v>402</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560181</t>
+          <t xml:space="preserve">311560182</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19B</t>
+          <t xml:space="preserve">Skolevej 21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6656,15 +6656,15 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J89">
-        <v>689</v>
+        <v>5032</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560185</t>
+          <t xml:space="preserve">311560184</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21</t>
+          <t xml:space="preserve">Skolevej 21B</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6731,15 +6731,15 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J90">
-        <v>402</v>
+        <v>560</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560182</t>
+          <t xml:space="preserve">311560186</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21</t>
+          <t xml:space="preserve">Skolevej 21D</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6806,15 +6806,15 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J91">
-        <v>5032</v>
+        <v>1198</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560184</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21B</t>
+          <t xml:space="preserve">Skolevej 23B</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6881,15 +6881,15 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>560</v>
+        <v>1583</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560186</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21D</t>
+          <t xml:space="preserve">Engelshøjgade 1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">8175481</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>1198</v>
+        <v>776</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560183</t>
+          <t xml:space="preserve">311560963</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 23B</t>
+          <t xml:space="preserve">Grundtvigs Alle 100</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J94">
-        <v>1583</v>
+        <v>9839</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560183</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelshøjgade 1</t>
+          <t xml:space="preserve">Grundtvigs Alle 100A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8175481</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="J95">
-        <v>776</v>
+        <v>487</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560963</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 100</t>
+          <t xml:space="preserve">Vestervej 42</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>9839</v>
+        <v>10333</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311568970</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 100A</t>
+          <t xml:space="preserve">Vestervej 42B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J97">
-        <v>487</v>
+        <v>3913</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311568975</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42</t>
+          <t xml:space="preserve">Vestervej 42D</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7331,15 +7331,15 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J98">
-        <v>10333</v>
+        <v>500</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568970</t>
+          <t xml:space="preserve">311568971</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42B</t>
+          <t xml:space="preserve">Primulavej 2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">5786366</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>3913</v>
+        <v>355</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568975</t>
+          <t xml:space="preserve">311652254</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,17 +7466,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42D</t>
+          <t xml:space="preserve">Grundtvigs Alle 150</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>500</v>
+        <v>6688</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568971</t>
+          <t xml:space="preserve">311661617</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,40 +7541,40 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primulavej 2</t>
+          <t xml:space="preserve">Grundtvigs Alle 150A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786366</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J101">
-        <v>355</v>
+        <v>975</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652254</t>
+          <t xml:space="preserve">311661616</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 150</t>
+          <t xml:space="preserve">Kløvermarken 1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,20 +7626,20 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">312395</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>6688</v>
+        <v>3239</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661617</t>
+          <t xml:space="preserve">311661619</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 150A</t>
+          <t xml:space="preserve">Sundsmarkvej 74</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,20 +7701,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">312396</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J103">
-        <v>975</v>
+        <v>4941</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661616</t>
+          <t xml:space="preserve">311661618</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 1</t>
+          <t xml:space="preserve">Gyden 96</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">312395</t>
+          <t xml:space="preserve">5290028</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,21 +7785,21 @@
         </is>
       </c>
       <c r="J104">
-        <v>3239</v>
+        <v>3620</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661619</t>
+          <t xml:space="preserve">311674038</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,40 +7841,40 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundsmarkvej 74</t>
+          <t xml:space="preserve">Gyden 96</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">312396</t>
+          <t xml:space="preserve">5290028</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J105">
-        <v>4941</v>
+        <v>1433</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661618</t>
+          <t xml:space="preserve">311674038</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyden 96</t>
+          <t xml:space="preserve">Gyden 96A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J106">
-        <v>3620</v>
+        <v>281</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyden 96</t>
+          <t xml:space="preserve">Kaplenivej 3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290028</t>
+          <t xml:space="preserve">9022207</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>1433</v>
+        <v>5131</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674521</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyden 96A</t>
+          <t xml:space="preserve">Kaplenivej 3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290028</t>
+          <t xml:space="preserve">9022207</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J108">
-        <v>281</v>
+        <v>5091</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674521</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J109">
-        <v>5131</v>
+        <v>775</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,30 +8216,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaplenivej 3</t>
+          <t xml:space="preserve">Vestergade 17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022207</t>
+          <t xml:space="preserve">5275405</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>5091</v>
+        <v>1266</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674521</t>
+          <t xml:space="preserve">311675319</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-18</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaplenivej 3</t>
+          <t xml:space="preserve">Vestergade 17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022207</t>
+          <t xml:space="preserve">5275405</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J111">
-        <v>775</v>
+        <v>1041</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674521</t>
+          <t xml:space="preserve">311675319</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-18</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J112">
-        <v>1266</v>
+        <v>831</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J113">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J114">
-        <v>831</v>
+        <v>2025</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J115">
-        <v>1054</v>
+        <v>331</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8681,11 +8681,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J116">
-        <v>2025</v>
+        <v>684</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 17</t>
+          <t xml:space="preserve">Nejsvej 19</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275405</t>
+          <t xml:space="preserve">5276459</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J117">
-        <v>331</v>
+        <v>1833</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675319</t>
+          <t xml:space="preserve">311677211</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 17</t>
+          <t xml:space="preserve">Nejsvej 19</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275405</t>
+          <t xml:space="preserve">5276459</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J118">
-        <v>684</v>
+        <v>1297</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675319</t>
+          <t xml:space="preserve">311677211</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 19</t>
+          <t xml:space="preserve">Nejsvej 19A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J119">
-        <v>1833</v>
+        <v>702</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677211</t>
+          <t xml:space="preserve">311677608</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-28</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 19</t>
+          <t xml:space="preserve">Nejsvej 21</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8981,15 +8981,15 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>1297</v>
+        <v>490</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677211</t>
+          <t xml:space="preserve">311677640</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-28</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 19A</t>
+          <t xml:space="preserve">Kettingvej 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5276459</t>
+          <t xml:space="preserve">8954042</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>702</v>
+        <v>1345</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677608</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 21</t>
+          <t xml:space="preserve">Kettingvej 1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5276459</t>
+          <t xml:space="preserve">8954042</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J122">
-        <v>490</v>
+        <v>725</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677640</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1</t>
+          <t xml:space="preserve">Kettingvej 1A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9206,11 +9206,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>1345</v>
+        <v>822</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1</t>
+          <t xml:space="preserve">Kettingvej 1C</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9281,15 +9281,15 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="J124">
-        <v>725</v>
+        <v>462</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1A</t>
+          <t xml:space="preserve">Kettingvej 1D</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,15 +9356,15 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J125">
-        <v>822</v>
+        <v>1707</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1C</t>
+          <t xml:space="preserve">Kettingvej 1E</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9431,15 +9431,15 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J126">
-        <v>462</v>
+        <v>1906</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1D</t>
+          <t xml:space="preserve">Kettingvej 1F</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9506,11 +9506,11 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J127">
-        <v>1707</v>
+        <v>2353</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1E</t>
+          <t xml:space="preserve">Kettingvej 1F</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J128">
-        <v>1906</v>
+        <v>1691</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1F</t>
+          <t xml:space="preserve">Stadionvej 8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9656,15 +9656,15 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="J129">
-        <v>2353</v>
+        <v>390</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686708</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1F</t>
+          <t xml:space="preserve">Arnkilgade 74</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8954042</t>
+          <t xml:space="preserve">5292219</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J130">
-        <v>1691</v>
+        <v>1110</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311690728</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-09</t>
+          <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,40 +9791,40 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 8</t>
+          <t xml:space="preserve">Arnkilgade 74</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8954042</t>
+          <t xml:space="preserve">5292219</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J131">
-        <v>390</v>
+        <v>1045</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686708</t>
+          <t xml:space="preserve">311690729</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-09</t>
+          <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnkilgade 74</t>
+          <t xml:space="preserve">Kystvej 1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292219</t>
+          <t xml:space="preserve">5257652</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="J132">
-        <v>1110</v>
+        <v>531</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690728</t>
+          <t xml:space="preserve">311692727</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-26</t>
+          <t xml:space="preserve">2033-07-04</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,40 +9941,40 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnkilgade 74</t>
+          <t xml:space="preserve">Kystvej 1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292219</t>
+          <t xml:space="preserve">5257652</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>1045</v>
+        <v>6400</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690729</t>
+          <t xml:space="preserve">311693153</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-26</t>
+          <t xml:space="preserve">2033-07-05</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystvej 1</t>
+          <t xml:space="preserve">Degnevænget 2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,30 +10026,30 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257652</t>
+          <t xml:space="preserve">5257645</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>531</v>
+        <v>2539</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692727</t>
+          <t xml:space="preserve">311696049</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-04</t>
+          <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystvej 1</t>
+          <t xml:space="preserve">Degnevænget 2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,30 +10101,30 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257652</t>
+          <t xml:space="preserve">5257645</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>6400</v>
+        <v>1312</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311693153</t>
+          <t xml:space="preserve">311696049</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-05</t>
+          <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10181,15 +10181,15 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J136">
-        <v>2539</v>
+        <v>1233</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696049</t>
+          <t xml:space="preserve">311696243</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-20</t>
+          <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2</t>
+          <t xml:space="preserve">Degnevænget 2E</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10256,15 +10256,15 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J137">
-        <v>1312</v>
+        <v>1981</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696049</t>
+          <t xml:space="preserve">311696280</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-20</t>
+          <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2</t>
+          <t xml:space="preserve">Johs Kochsvej 16</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10331,15 +10331,15 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>1233</v>
+        <v>2210</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696243</t>
+          <t xml:space="preserve">311696184</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2E</t>
+          <t xml:space="preserve">Degnevænget 2C</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,15 +10406,15 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J139">
-        <v>1981</v>
+        <v>501</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696280</t>
+          <t xml:space="preserve">311696375</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-21</t>
+          <t xml:space="preserve">2033-07-24</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johs Kochsvej 16</t>
+          <t xml:space="preserve">Johs Kochsvej 12</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10481,15 +10481,15 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J140">
-        <v>2210</v>
+        <v>252</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696184</t>
+          <t xml:space="preserve">311697270</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-21</t>
+          <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2C</t>
+          <t xml:space="preserve">Johs Kochsvej 14</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10556,15 +10556,15 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J141">
-        <v>501</v>
+        <v>737</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696375</t>
+          <t xml:space="preserve">311697276</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-24</t>
+          <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johs Kochsvej 12</t>
+          <t xml:space="preserve">Gammel Aabenraavej 24</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257645</t>
+          <t xml:space="preserve">5784337</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>252</v>
+        <v>5859</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697270</t>
+          <t xml:space="preserve">311698797</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-31</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborg Kommune</t>
+          <t xml:space="preserve">Boligforeningen B42</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johs Kochsvej 14</t>
+          <t xml:space="preserve">Storegade 6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257645</t>
+          <t xml:space="preserve">307811, 307812, 307813, 307814, 307815</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>737</v>
+        <v>2001</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697276</t>
+          <t xml:space="preserve">311698761</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-31</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 24</t>
+          <t xml:space="preserve">Skovvej 2A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,30 +10776,30 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784337</t>
+          <t xml:space="preserve">5782338</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J144">
-        <v>5859</v>
+        <v>5091</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698797</t>
+          <t xml:space="preserve">311717581</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Total-Tjek</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligforeningen B42</t>
+          <t xml:space="preserve">Sønderborg Kommune</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10841,40 +10841,40 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 6</t>
+          <t xml:space="preserve">Skovvej 2A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">307811, 307812, 307813, 307814, 307815</t>
+          <t xml:space="preserve">5782338</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J145">
-        <v>2001</v>
+        <v>800</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698761</t>
+          <t xml:space="preserve">311717585</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Total-Tjek</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 2A</t>
+          <t xml:space="preserve">Skovvej 4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5782338</t>
+          <t xml:space="preserve">7181513</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>5091</v>
+        <v>267</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717581</t>
+          <t xml:space="preserve">311717579</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,40 +10991,40 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 2A</t>
+          <t xml:space="preserve">Ahlefeldvej 4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5782338</t>
+          <t xml:space="preserve">5257481</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>800</v>
+        <v>4554</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717585</t>
+          <t xml:space="preserve">311758410</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total-Tjek</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,40 +11066,40 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 4</t>
+          <t xml:space="preserve">Ahlefeldvej 4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7181513</t>
+          <t xml:space="preserve">5257481</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J148">
-        <v>267</v>
+        <v>397</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717579</t>
+          <t xml:space="preserve">311758410</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total-Tjek</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldvej 4</t>
+          <t xml:space="preserve">Allegade 4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257481</t>
+          <t xml:space="preserve">5275746</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>4554</v>
+        <v>1497</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758410</t>
+          <t xml:space="preserve">311758407</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,40 +11216,40 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldvej 4</t>
+          <t xml:space="preserve">Flintevænget 67</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257481</t>
+          <t xml:space="preserve">5294810</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>397</v>
+        <v>570</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758410</t>
+          <t xml:space="preserve">311761633</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 4</t>
+          <t xml:space="preserve">Gammel Guderup 31</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275746</t>
+          <t xml:space="preserve">5294806</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,21 +11310,21 @@
         </is>
       </c>
       <c r="J151">
-        <v>1497</v>
+        <v>617</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758407</t>
+          <t xml:space="preserve">311761630</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintevænget 67</t>
+          <t xml:space="preserve">Nørreled 31</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294810</t>
+          <t xml:space="preserve">7846650</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761633</t>
+          <t xml:space="preserve">311761632</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Guderup 31</t>
+          <t xml:space="preserve">Nørreled 31</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294806</t>
+          <t xml:space="preserve">7846650</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>617</v>
+        <v>1220</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761630</t>
+          <t xml:space="preserve">311761632</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreled 31</t>
+          <t xml:space="preserve">Bakkensbro 6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7846650</t>
+          <t xml:space="preserve">5281873</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="J154">
-        <v>597</v>
+        <v>1305</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761632</t>
+          <t xml:space="preserve">311762260</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-24</t>
+          <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreled 31</t>
+          <t xml:space="preserve">Bakkensbro 6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7846650</t>
+          <t xml:space="preserve">5281873</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,21 +11610,21 @@
         </is>
       </c>
       <c r="J155">
-        <v>1220</v>
+        <v>429</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761632</t>
+          <t xml:space="preserve">311762260</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-24</t>
+          <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkensbro 6</t>
+          <t xml:space="preserve">Bakkensbro 8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J156">
-        <v>1305</v>
+        <v>592</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkensbro 6</t>
+          <t xml:space="preserve">Hølle Vej 4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281873</t>
+          <t xml:space="preserve">8955245</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>429</v>
+        <v>1449</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762260</t>
+          <t xml:space="preserve">311762253</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkensbro 8</t>
+          <t xml:space="preserve">Skovgade 13</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281873</t>
+          <t xml:space="preserve">8955245</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>592</v>
+        <v>6013</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762260</t>
+          <t xml:space="preserve">311762255</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,40 +11891,40 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hølle Vej 4</t>
+          <t xml:space="preserve">Skolegade 21</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955245</t>
+          <t xml:space="preserve">5294181</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>1449</v>
+        <v>2590</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762253</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,40 +11966,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgade 13</t>
+          <t xml:space="preserve">Skolegade 21</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955245</t>
+          <t xml:space="preserve">5294181</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J160">
-        <v>6013</v>
+        <v>606</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762255</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 21</t>
+          <t xml:space="preserve">Skolegade 23</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,11 +12056,11 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J161">
-        <v>2590</v>
+        <v>4077</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 21</t>
+          <t xml:space="preserve">Skolegade 23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J162">
-        <v>606</v>
+        <v>1160</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311766887</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 23</t>
+          <t xml:space="preserve">Skolegade 9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12206,15 +12206,15 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J163">
-        <v>4077</v>
+        <v>329</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311766886</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 23</t>
+          <t xml:space="preserve">Luffes Plads 2</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294181</t>
+          <t xml:space="preserve">9562993</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J164">
-        <v>1160</v>
+        <v>1425</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766887</t>
+          <t xml:space="preserve">311771819</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 9</t>
+          <t xml:space="preserve">Dalsmark 13</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294181</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>329</v>
+        <v>2404</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766886</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,30 +12416,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luffes Plads 2</t>
+          <t xml:space="preserve">Dalsmark 13</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562993</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J166">
-        <v>1425</v>
+        <v>676</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771819</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-05</t>
+          <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J167">
-        <v>2404</v>
+        <v>690</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsmark 13</t>
+          <t xml:space="preserve">Højløkke 2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">8515752</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>676</v>
+        <v>532</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788047</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsmark 13</t>
+          <t xml:space="preserve">Stenvej 10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">5272155</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>690</v>
+        <v>1794</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788055</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højløkke 2</t>
+          <t xml:space="preserve">Stenvej 10C</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8515752</t>
+          <t xml:space="preserve">5272155</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J170">
-        <v>532</v>
+        <v>779</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788047</t>
+          <t xml:space="preserve">311788056</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 10</t>
+          <t xml:space="preserve">Stenvej 28</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272155</t>
+          <t xml:space="preserve">5272862</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>1794</v>
+        <v>533</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788055</t>
+          <t xml:space="preserve">311788048</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,30 +12866,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 10C</t>
+          <t xml:space="preserve">Luffes Plads 4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272155</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J172">
-        <v>779</v>
+        <v>266</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788056</t>
+          <t xml:space="preserve">311797325</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-27</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,17 +12941,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 28</t>
+          <t xml:space="preserve">Peblingestien 2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272862</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>533</v>
+        <v>1764</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788048</t>
+          <t xml:space="preserve">311797326</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-27</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luffes Plads 4</t>
+          <t xml:space="preserve">Peblingestien 2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13031,15 +13031,15 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J174">
-        <v>266</v>
+        <v>1210</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797325</t>
+          <t xml:space="preserve">311797324</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13106,15 +13106,15 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J175">
-        <v>1764</v>
+        <v>1828</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797326</t>
+          <t xml:space="preserve">311797324</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J176">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peblingestien 2</t>
+          <t xml:space="preserve">Industrivej 5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">5278117</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>1828</v>
+        <v>745</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797324</t>
+          <t xml:space="preserve">311799237</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-11-25</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peblingestien 2</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20B</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J178">
-        <v>1210</v>
+        <v>609</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797324</t>
+          <t xml:space="preserve">311800215</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 5</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20C</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278117</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J179">
-        <v>745</v>
+        <v>2643</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311799237</t>
+          <t xml:space="preserve">311800213</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-25</t>
+          <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20B</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20E</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,15 +13481,15 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J180">
-        <v>609</v>
+        <v>2605</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800215</t>
+          <t xml:space="preserve">311800217</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20C</t>
+          <t xml:space="preserve">Dybbølsten 29</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">5279082</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>2643</v>
+        <v>382</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800213</t>
+          <t xml:space="preserve">311803358</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-29</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20E</t>
+          <t xml:space="preserve">Gammeldam 2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">8940680</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>2605</v>
+        <v>485</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800217</t>
+          <t xml:space="preserve">311803387</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-29</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dybbølsten 29</t>
+          <t xml:space="preserve">Kirke Alle 9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5279082</t>
+          <t xml:space="preserve">5781025</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>382</v>
+        <v>1339</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803358</t>
+          <t xml:space="preserve">311803378</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammeldam 2</t>
+          <t xml:space="preserve">Kirke Alle 9A</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940680</t>
+          <t xml:space="preserve">5781025</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J184">
-        <v>485</v>
+        <v>317</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803387</t>
+          <t xml:space="preserve">311803381</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 9</t>
+          <t xml:space="preserve">Kongevej 19</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781025</t>
+          <t xml:space="preserve">1512200</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>1339</v>
+        <v>2901</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803378</t>
+          <t xml:space="preserve">311803350</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 9A</t>
+          <t xml:space="preserve">Løjtertoft 32</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781025</t>
+          <t xml:space="preserve">5787147</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803381</t>
+          <t xml:space="preserve">311803395</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,17 +13991,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 19</t>
+          <t xml:space="preserve">Mads Clausens Vej 103</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512200</t>
+          <t xml:space="preserve">8995417</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>2901</v>
+        <v>604</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803350</t>
+          <t xml:space="preserve">311803386</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjtertoft 32</t>
+          <t xml:space="preserve">Mads Clausens Vej 13</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787147</t>
+          <t xml:space="preserve">5787761</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>385</v>
+        <v>4402</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803395</t>
+          <t xml:space="preserve">311803385</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 103</t>
+          <t xml:space="preserve">Martin Nyrops Plads 2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995417</t>
+          <t xml:space="preserve">5781423</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>604</v>
+        <v>1859</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803386</t>
+          <t xml:space="preserve">311803364</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 13</t>
+          <t xml:space="preserve">Palmose 14</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787761</t>
+          <t xml:space="preserve">5278572</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>4402</v>
+        <v>917</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803385</t>
+          <t xml:space="preserve">311803369</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Nyrops Plads 2</t>
+          <t xml:space="preserve">Drosselvænget 1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781423</t>
+          <t xml:space="preserve">5275696</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>1859</v>
+        <v>385</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803364</t>
+          <t xml:space="preserve">311803590</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palmose 14</t>
+          <t xml:space="preserve">Mellemvej 16</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278572</t>
+          <t xml:space="preserve">5787784</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>917</v>
+        <v>868</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803369</t>
+          <t xml:space="preserve">311803725</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvænget 1</t>
+          <t xml:space="preserve">Mosevej 1A</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275696</t>
+          <t xml:space="preserve">5294114</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>385</v>
+        <v>288</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803590</t>
+          <t xml:space="preserve">311803601</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvej 16</t>
+          <t xml:space="preserve">Stavensbølgade 66</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787784</t>
+          <t xml:space="preserve">5286834</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>868</v>
+        <v>365</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803725</t>
+          <t xml:space="preserve">311809080</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-19</t>
+          <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,30 +14591,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 1A</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26B</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294114</t>
+          <t xml:space="preserve">5784905</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J195">
-        <v>288</v>
+        <v>1592</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803601</t>
+          <t xml:space="preserve">311809344</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-19</t>
+          <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavensbølgade 66</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26C</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5286834</t>
+          <t xml:space="preserve">5784905</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J196">
-        <v>365</v>
+        <v>476</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809080</t>
+          <t xml:space="preserve">311809346</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26B</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26D</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,15 +14756,15 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>1592</v>
+        <v>496</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809344</t>
+          <t xml:space="preserve">311809350</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26C</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26E</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J198">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809346</t>
+          <t xml:space="preserve">311809348</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26D</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26G</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14906,15 +14906,15 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J199">
-        <v>496</v>
+        <v>302</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809350</t>
+          <t xml:space="preserve">311809353</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26E</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 28</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14981,15 +14981,15 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J200">
-        <v>476</v>
+        <v>406</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809348</t>
+          <t xml:space="preserve">311809345</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26G</t>
+          <t xml:space="preserve">Friheds Alle 45A</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,30 +15051,30 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784905</t>
+          <t xml:space="preserve">5785197</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>302</v>
+        <v>460</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809353</t>
+          <t xml:space="preserve">311815182</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-03</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborg Kommune</t>
+          <t xml:space="preserve">HØRUP MENIGHEDSRÅD</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -15116,40 +15116,40 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 28</t>
+          <t xml:space="preserve">Hørup Bygade 14</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784905</t>
+          <t xml:space="preserve">735599, 9159257</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J202">
-        <v>406</v>
+        <v>277</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809345</t>
+          <t xml:space="preserve">311815184</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-03</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,17 +15191,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friheds Alle 45A</t>
+          <t xml:space="preserve">Kløverlykke 31</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785197</t>
+          <t xml:space="preserve">8227241</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15210,11 +15210,11 @@
         </is>
       </c>
       <c r="J203">
-        <v>460</v>
+        <v>343</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815182</t>
+          <t xml:space="preserve">311815183</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15251,12 +15251,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">HØRUP MENIGHEDSRÅD</t>
+          <t xml:space="preserve">Sønderborg Kommune</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -15266,40 +15266,40 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørup Bygade 14</t>
+          <t xml:space="preserve">Skovvej 16</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">735599, 9159257</t>
+          <t xml:space="preserve">5785311</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>277</v>
+        <v>1956</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815184</t>
+          <t xml:space="preserve">311821475</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløverlykke 31</t>
+          <t xml:space="preserve">Lysabildgade 2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8227241</t>
+          <t xml:space="preserve">5287561</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,21 +15360,21 @@
         </is>
       </c>
       <c r="J205">
-        <v>343</v>
+        <v>3893</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815183</t>
+          <t xml:space="preserve">311823018</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-04-05</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,17 +15416,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 16</t>
+          <t xml:space="preserve">Knøs' Gård 1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785311</t>
+          <t xml:space="preserve">5285296</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,11 +15435,11 @@
         </is>
       </c>
       <c r="J206">
-        <v>1956</v>
+        <v>313</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821475</t>
+          <t xml:space="preserve">311838372</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-31</t>
+          <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysabildgade 2</t>
+          <t xml:space="preserve">Knøs' Gård 1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,20 +15501,20 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287561</t>
+          <t xml:space="preserve">5285296</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J207">
-        <v>3893</v>
+        <v>298</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823018</t>
+          <t xml:space="preserve">311838372</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-05</t>
+          <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15581,11 +15581,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J208">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knøs' Gård 1</t>
+          <t xml:space="preserve">Lille Rådhusgade 7</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285296</t>
+          <t xml:space="preserve">5780820</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>298</v>
+        <v>1838</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838372</t>
+          <t xml:space="preserve">311838476</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,30 +15716,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knøs' Gård 1</t>
+          <t xml:space="preserve">Parkgade 54</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285296</t>
+          <t xml:space="preserve">10140604</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J210">
-        <v>293</v>
+        <v>690</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838372</t>
+          <t xml:space="preserve">311838368</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Rådhusgade 7</t>
+          <t xml:space="preserve">Vothmanns Plads 2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15806,11 +15806,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J211">
-        <v>1838</v>
+        <v>2577</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15866,40 +15866,40 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkgade 54</t>
+          <t xml:space="preserve">Sundgade 100</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">10140604</t>
+          <t xml:space="preserve">5283387</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>690</v>
+        <v>1275</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838368</t>
+          <t xml:space="preserve">311872709</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-16</t>
+          <t xml:space="preserve">2035-12-10</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vothmanns Plads 2</t>
+          <t xml:space="preserve">Huholt 13</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,30 +15951,30 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780820</t>
+          <t xml:space="preserve">5293106</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>2577</v>
+        <v>309</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838476</t>
+          <t xml:space="preserve">311874211</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-16</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundgade 100</t>
+          <t xml:space="preserve">Piledamsvej 4</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5283387</t>
+          <t xml:space="preserve">5295339</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>1275</v>
+        <v>625</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872709</t>
+          <t xml:space="preserve">311874110</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-10</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huholt 13</t>
+          <t xml:space="preserve">Piledamsvej 4C</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5293106</t>
+          <t xml:space="preserve">5295340</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>309</v>
+        <v>664</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874211</t>
+          <t xml:space="preserve">311874111</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,17 +16166,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledamsvej 4</t>
+          <t xml:space="preserve">Katforte 20</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295339</t>
+          <t xml:space="preserve">5280052</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>625</v>
+        <v>2377</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874110</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledamsvej 4C</t>
+          <t xml:space="preserve">Katforte 20</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295340</t>
+          <t xml:space="preserve">5280052</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J217">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874111</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katforte 20</t>
+          <t xml:space="preserve">Sundsmarkvej 72</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280052</t>
+          <t xml:space="preserve">5783504</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J218">
-        <v>2377</v>
+        <v>307</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874745</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2035-12-22</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,30 +16391,30 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katforte 20</t>
+          <t xml:space="preserve">Illerstrandvej 7</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280052</t>
+          <t xml:space="preserve">8955105</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J219">
-        <v>648</v>
+        <v>1284</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874954</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2035-12-29</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,40 +16466,40 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundsmarkvej 72</t>
+          <t xml:space="preserve">Tangshave 1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783504</t>
+          <t xml:space="preserve">5786913</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>307</v>
+        <v>3416</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874745</t>
+          <t xml:space="preserve">311880881</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-22</t>
+          <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,40 +16541,40 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Illerstrandvej 7</t>
+          <t xml:space="preserve">Tangshave 3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955105</t>
+          <t xml:space="preserve">5786913</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>1284</v>
+        <v>1454</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874954</t>
+          <t xml:space="preserve">311880883</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-29</t>
+          <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 1</t>
+          <t xml:space="preserve">Tangshave 5</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,15 +16631,15 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J222">
-        <v>3416</v>
+        <v>725</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880881</t>
+          <t xml:space="preserve">311880886</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 3</t>
+          <t xml:space="preserve">Tangshave 6</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,15 +16706,15 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J223">
-        <v>1454</v>
+        <v>725</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880883</t>
+          <t xml:space="preserve">311880886</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 5</t>
+          <t xml:space="preserve">Tangshave 7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J224">
-        <v>725</v>
+        <v>501</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 6</t>
+          <t xml:space="preserve">Tangshave 8</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J225">
-        <v>725</v>
+        <v>501</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 7</t>
+          <t xml:space="preserve">Tangshave 9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,20 +16926,20 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786913</t>
+          <t xml:space="preserve">9883339</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J226">
-        <v>501</v>
+        <v>758</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880886</t>
+          <t xml:space="preserve">311880882</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 8</t>
+          <t xml:space="preserve">Egen Markvej 6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786913</t>
+          <t xml:space="preserve">9151675</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J227">
-        <v>501</v>
+        <v>729</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880886</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-06</t>
+          <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 9</t>
+          <t xml:space="preserve">Egen Markvej 8</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,30 +17076,30 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883339</t>
+          <t xml:space="preserve">9151675</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>758</v>
+        <v>282</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880882</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-06</t>
+          <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,40 +17141,40 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egen Markvej 6</t>
+          <t xml:space="preserve">Hørup Bygade 44A</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151675</t>
+          <t xml:space="preserve">308336, 308337</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>729</v>
+        <v>4431</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884429</t>
+          <t xml:space="preserve">311884501</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-26</t>
+          <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,40 +17216,40 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egen Markvej 8</t>
+          <t xml:space="preserve">Hørup Bygade 44C</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151675</t>
+          <t xml:space="preserve">8917471</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J230">
-        <v>282</v>
+        <v>882</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884427</t>
+          <t xml:space="preserve">311884502</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-26</t>
+          <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørup Bygade 44A</t>
+          <t xml:space="preserve">Hørup Bygade 44D</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,20 +17301,20 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">308336, 308337</t>
+          <t xml:space="preserve">8917471</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J231">
-        <v>4431</v>
+        <v>840</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884501</t>
+          <t xml:space="preserve">311884502</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørup Bygade 44C</t>
+          <t xml:space="preserve">Tandsbjerg 10</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917471</t>
+          <t xml:space="preserve">5784983</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>882</v>
+        <v>8047</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884502</t>
+          <t xml:space="preserve">311890301</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-27</t>
+          <t xml:space="preserve">2036-03-26</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,30 +17441,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørup Bygade 44D</t>
+          <t xml:space="preserve">Bosager 2</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917471</t>
+          <t xml:space="preserve">9844747</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>840</v>
+        <v>1107</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884502</t>
+          <t xml:space="preserve">311892951</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-27</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tandsbjerg 10</t>
+          <t xml:space="preserve">Bosager 4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,20 +17526,20 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784983</t>
+          <t xml:space="preserve">9844747</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J234">
-        <v>8047</v>
+        <v>3320</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890301</t>
+          <t xml:space="preserve">311892952</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-26</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bosager 2</t>
+          <t xml:space="preserve">Bosager 8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17606,15 +17606,15 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J235">
-        <v>1107</v>
+        <v>1456</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892951</t>
+          <t xml:space="preserve">311892953</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17666,40 +17666,40 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bosager 4</t>
+          <t xml:space="preserve">Skolevænget 16</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844747</t>
+          <t xml:space="preserve">5298409</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>3320</v>
+        <v>850</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892952</t>
+          <t xml:space="preserve">311896959</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bosager 8</t>
+          <t xml:space="preserve">Kettingvej 24</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844747</t>
+          <t xml:space="preserve">5785944</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>1456</v>
+        <v>3262</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892953</t>
+          <t xml:space="preserve">311900364</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,40 +17816,40 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 16</t>
+          <t xml:space="preserve">Kettingvej 24A</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298409</t>
+          <t xml:space="preserve">5786709</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J238">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896959</t>
+          <t xml:space="preserve">311900368</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 24</t>
+          <t xml:space="preserve">Parkgade 15</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785944</t>
+          <t xml:space="preserve">8187423</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,11 +17910,11 @@
         </is>
       </c>
       <c r="J239">
-        <v>3262</v>
+        <v>299</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900364</t>
+          <t xml:space="preserve">311900365</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 24A</t>
+          <t xml:space="preserve">Østergade 10</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J240">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkgade 15</t>
+          <t xml:space="preserve">Østergade 20</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,20 +18051,20 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187423</t>
+          <t xml:space="preserve">5786709</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900365</t>
+          <t xml:space="preserve">311900368</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 10</t>
+          <t xml:space="preserve">Østergade 8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786709</t>
+          <t xml:space="preserve">5786710</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -18135,11 +18135,11 @@
         </is>
       </c>
       <c r="J242">
-        <v>300</v>
+        <v>2009</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900368</t>
+          <t xml:space="preserve">311900366</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 20</t>
+          <t xml:space="preserve">Notmark 46</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,30 +18201,30 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786709</t>
+          <t xml:space="preserve">8082746</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J243">
-        <v>300</v>
+        <v>483</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900368</t>
+          <t xml:space="preserve">311902104</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-11</t>
+          <t xml:space="preserve">2036-05-19</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,17 +18266,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 8</t>
+          <t xml:space="preserve">Porsgrunngade 4</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786710</t>
+          <t xml:space="preserve">5785227</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,21 +18285,21 @@
         </is>
       </c>
       <c r="J244">
-        <v>2009</v>
+        <v>377</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900366</t>
+          <t xml:space="preserve">311902483</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-11</t>
+          <t xml:space="preserve">2036-05-20</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,17 +18341,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notmark 46</t>
+          <t xml:space="preserve">Damgade 5</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">8082746</t>
+          <t xml:space="preserve">5783261</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,21 +18360,21 @@
         </is>
       </c>
       <c r="J245">
-        <v>483</v>
+        <v>3061</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902104</t>
+          <t xml:space="preserve">311903722</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-19</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Porsgrunngade 4</t>
+          <t xml:space="preserve">Møllevang 6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785227</t>
+          <t xml:space="preserve">5783261</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J246">
-        <v>377</v>
+        <v>2390</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902483</t>
+          <t xml:space="preserve">311903722</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-20</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damgade 5</t>
+          <t xml:space="preserve">Ved Mølledammen 18</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18506,11 +18506,11 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J247">
-        <v>3061</v>
+        <v>1773</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevang 6</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,30 +18576,30 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783261</t>
+          <t xml:space="preserve">5280813</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>2390</v>
+        <v>274</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903722</t>
+          <t xml:space="preserve">311904401</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-05-28</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Mølledammen 18</t>
+          <t xml:space="preserve">Videnvej 2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,30 +18651,30 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783261</t>
+          <t xml:space="preserve">5280150</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J249">
-        <v>1773</v>
+        <v>2630</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903722</t>
+          <t xml:space="preserve">311905047</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,17 +18716,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Skolevænget 14</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280813</t>
+          <t xml:space="preserve">5298339</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -18735,11 +18735,11 @@
         </is>
       </c>
       <c r="J250">
-        <v>274</v>
+        <v>643</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904401</t>
+          <t xml:space="preserve">311907808</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-28</t>
+          <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,17 +18791,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Videnvej 2</t>
+          <t xml:space="preserve">Engparken 4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280150</t>
+          <t xml:space="preserve">5258097</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -18810,21 +18810,21 @@
         </is>
       </c>
       <c r="J251">
-        <v>2630</v>
+        <v>503</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905047</t>
+          <t xml:space="preserve">311910650</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-24</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,17 +18866,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 14</t>
+          <t xml:space="preserve">Engparken 6</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298339</t>
+          <t xml:space="preserve">5258413</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -18885,21 +18885,21 @@
         </is>
       </c>
       <c r="J252">
-        <v>643</v>
+        <v>464</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907808</t>
+          <t xml:space="preserve">311910651</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-12</t>
+          <t xml:space="preserve">2036-06-24</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,17 +18941,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engparken 4</t>
+          <t xml:space="preserve">Solskrænten 26</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5258097</t>
+          <t xml:space="preserve">5276117</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -18960,11 +18960,11 @@
         </is>
       </c>
       <c r="J253">
-        <v>503</v>
+        <v>448</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910650</t>
+          <t xml:space="preserve">311910416</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engparken 6</t>
+          <t xml:space="preserve">Dyrkobbelgård Allé 4</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5258413</t>
+          <t xml:space="preserve">8527991</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,11 +19035,11 @@
         </is>
       </c>
       <c r="J254">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910651</t>
+          <t xml:space="preserve">311914417</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-24</t>
+          <t xml:space="preserve">2036-07-13</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solskrænten 26</t>
+          <t xml:space="preserve">Nejs Møllevej 15</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5276117</t>
+          <t xml:space="preserve">5277912</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -19110,11 +19110,11 @@
         </is>
       </c>
       <c r="J255">
-        <v>448</v>
+        <v>612</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910416</t>
+          <t xml:space="preserve">311914415</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-24</t>
+          <t xml:space="preserve">2036-07-13</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrkobbelgård Allé 4</t>
+          <t xml:space="preserve">Ravnsbjergvej 12</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8527991</t>
+          <t xml:space="preserve">8078774</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>532</v>
+        <v>720</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914417</t>
+          <t xml:space="preserve">311914414</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19241,40 +19241,40 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejs Møllevej 15</t>
+          <t xml:space="preserve">Gerlachsgade 3</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5277912</t>
+          <t xml:space="preserve">9022269</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J257">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914415</t>
+          <t xml:space="preserve">311920169</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-13</t>
+          <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsbjergvej 12</t>
+          <t xml:space="preserve">Gerlachsgade 5A</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8078774</t>
+          <t xml:space="preserve">9022269</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J258">
-        <v>720</v>
+        <v>9768</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914414</t>
+          <t xml:space="preserve">311920169</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-13</t>
+          <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerlachsgade 3</t>
+          <t xml:space="preserve">Nybølvej 2</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,25 +19401,25 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022269</t>
+          <t xml:space="preserve">5280837</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>624</v>
+        <v>1089</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920155</t>
+          <t xml:space="preserve">311920147</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -19466,35 +19466,35 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerlachsgade 5A</t>
+          <t xml:space="preserve">Tandsbusk 2</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022269</t>
+          <t xml:space="preserve">5290830</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>9768</v>
+        <v>285</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920155</t>
+          <t xml:space="preserve">311920174</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybølvej 2</t>
+          <t xml:space="preserve">Rådhustorvet 7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280837</t>
+          <t xml:space="preserve">5780676</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -19560,21 +19560,21 @@
         </is>
       </c>
       <c r="J261">
-        <v>1089</v>
+        <v>284</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920147</t>
+          <t xml:space="preserve">311921651</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-19</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,40 +19616,40 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tandsbusk 2</t>
+          <t xml:space="preserve">Ellegårdvej 36</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290830</t>
+          <t xml:space="preserve">735673, 7657845</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J262">
-        <v>285</v>
+        <v>2607</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920174</t>
+          <t xml:space="preserve">311922243</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-19</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhustorvet 7</t>
+          <t xml:space="preserve">Ellegårdvej 36</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780676</t>
+          <t xml:space="preserve">7657845</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -19710,11 +19710,11 @@
         </is>
       </c>
       <c r="J263">
-        <v>284</v>
+        <v>1390</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921651</t>
+          <t xml:space="preserve">311922243</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellegårdvej 36</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">735673, 7657845</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,11 +19785,11 @@
         </is>
       </c>
       <c r="J264">
-        <v>2607</v>
+        <v>4233</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922243</t>
+          <t xml:space="preserve">311924502</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellegårdvej 36</t>
+          <t xml:space="preserve">Nørrebro 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">7657845</t>
+          <t xml:space="preserve">100911120</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>1390</v>
+        <v>384</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922243</t>
+          <t xml:space="preserve">311924501</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-09-08</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20</t>
+          <t xml:space="preserve">Rådyrvej 1A</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,20 +19926,20 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">9665069</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J266">
-        <v>4233</v>
+        <v>686</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924502</t>
+          <t xml:space="preserve">311924632</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-09</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 1</t>
+          <t xml:space="preserve">Ringriderpladsen 5A</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,20 +20001,20 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">100911120</t>
+          <t xml:space="preserve">1512217</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J267">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924501</t>
+          <t xml:space="preserve">311925190</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-08</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,17 +20066,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådyrvej 1A</t>
+          <t xml:space="preserve">Bækvej 10</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665069</t>
+          <t xml:space="preserve">9151738</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,11 +20085,11 @@
         </is>
       </c>
       <c r="J268">
-        <v>686</v>
+        <v>362</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924632</t>
+          <t xml:space="preserve">311926074</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-09</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,30 +20141,30 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringriderpladsen 5A</t>
+          <t xml:space="preserve">Løjtertoft 7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512217</t>
+          <t xml:space="preserve">5787622</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J269">
-        <v>318</v>
+        <v>1001</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925190</t>
+          <t xml:space="preserve">311926075</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">

--- a/public/exports-with-coowners/29189773.xlsx
+++ b/public/exports-with-coowners/29189773.xlsx
@@ -16264,12 +16264,12 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884430</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900367</t>
+          <t xml:space="preserve">311900366</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
